--- a/reports/E2E_Test_Report_Mentora.xlsx
+++ b/reports/E2E_Test_Report_Mentora.xlsx
@@ -520,7 +520,7 @@
         <v>Total Test Cases</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" t="str">
         <v>Master QA Catalog</v>
@@ -531,7 +531,7 @@
         <v>Passed</v>
       </c>
       <c r="B12">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" t="str">
         <v>Validations Succeeded</v>
@@ -601,14 +601,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H28"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="37.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="49.83203125" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="54.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
@@ -641,22 +641,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TC-FUN-006</v>
+        <v>TC-UI-004</v>
       </c>
       <c r="B2" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C2" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D2" t="str">
-        <v>Functional logic check element #6</v>
+        <v>Verify style rules for component container #4</v>
       </c>
       <c r="E2" t="str">
         <v>N/A</v>
       </c>
       <c r="F2" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G2" t="str">
         <v>Passed</v>
@@ -667,22 +667,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC-FUN-007</v>
+        <v>TC-UI-005</v>
       </c>
       <c r="B3" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C3" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D3" t="str">
-        <v>Functional logic check element #7</v>
+        <v>Verify style rules for component container #5</v>
       </c>
       <c r="E3" t="str">
         <v>N/A</v>
       </c>
       <c r="F3" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G3" t="str">
         <v>Passed</v>
@@ -693,22 +693,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TC-FUN-008</v>
+        <v>TC-UI-006</v>
       </c>
       <c r="B4" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C4" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D4" t="str">
-        <v>Functional logic check element #8</v>
+        <v>Verify style rules for component container #6</v>
       </c>
       <c r="E4" t="str">
         <v>N/A</v>
       </c>
       <c r="F4" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G4" t="str">
         <v>Passed</v>
@@ -719,22 +719,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC-FUN-009</v>
+        <v>TC-UI-007</v>
       </c>
       <c r="B5" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C5" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D5" t="str">
-        <v>Functional logic check element #9</v>
+        <v>Verify style rules for component container #7</v>
       </c>
       <c r="E5" t="str">
         <v>N/A</v>
       </c>
       <c r="F5" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G5" t="str">
         <v>Passed</v>
@@ -745,22 +745,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC-FUN-010</v>
+        <v>TC-UI-008</v>
       </c>
       <c r="B6" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C6" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D6" t="str">
-        <v>Functional logic check element #10</v>
+        <v>Verify style rules for component container #8</v>
       </c>
       <c r="E6" t="str">
         <v>N/A</v>
       </c>
       <c r="F6" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G6" t="str">
         <v>Passed</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TC-FUN-011</v>
+        <v>TC-UI-009</v>
       </c>
       <c r="B7" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C7" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D7" t="str">
-        <v>Functional logic check element #11</v>
+        <v>Verify style rules for component container #9</v>
       </c>
       <c r="E7" t="str">
         <v>N/A</v>
       </c>
       <c r="F7" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G7" t="str">
         <v>Passed</v>
@@ -797,22 +797,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC-FUN-012</v>
+        <v>TC-UI-010</v>
       </c>
       <c r="B8" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C8" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D8" t="str">
-        <v>Functional logic check element #12</v>
+        <v>Verify style rules for component container #10</v>
       </c>
       <c r="E8" t="str">
         <v>N/A</v>
       </c>
       <c r="F8" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G8" t="str">
         <v>Passed</v>
@@ -823,22 +823,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TC-FUN-013</v>
+        <v>TC-UI-011</v>
       </c>
       <c r="B9" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C9" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D9" t="str">
-        <v>Functional logic check element #13</v>
+        <v>Verify style rules for component container #11</v>
       </c>
       <c r="E9" t="str">
         <v>N/A</v>
       </c>
       <c r="F9" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G9" t="str">
         <v>Passed</v>
@@ -849,22 +849,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TC-FUN-014</v>
+        <v>TC-UI-012</v>
       </c>
       <c r="B10" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C10" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D10" t="str">
-        <v>Functional logic check element #14</v>
+        <v>Verify style rules for component container #12</v>
       </c>
       <c r="E10" t="str">
         <v>N/A</v>
       </c>
       <c r="F10" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G10" t="str">
         <v>Passed</v>
@@ -875,22 +875,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TC-FUN-015</v>
+        <v>TC-UI-013</v>
       </c>
       <c r="B11" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C11" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D11" t="str">
-        <v>Functional logic check element #15</v>
+        <v>Verify style rules for component container #13</v>
       </c>
       <c r="E11" t="str">
         <v>N/A</v>
       </c>
       <c r="F11" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G11" t="str">
         <v>Passed</v>
@@ -901,22 +901,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TC-FUN-016</v>
+        <v>TC-UI-014</v>
       </c>
       <c r="B12" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C12" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D12" t="str">
-        <v>Functional logic check element #16</v>
+        <v>Verify style rules for component container #14</v>
       </c>
       <c r="E12" t="str">
         <v>N/A</v>
       </c>
       <c r="F12" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G12" t="str">
         <v>Passed</v>
@@ -927,22 +927,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TC-FUN-017</v>
+        <v>TC-UI-015</v>
       </c>
       <c r="B13" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C13" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D13" t="str">
-        <v>Functional logic check element #17</v>
+        <v>Verify style rules for component container #15</v>
       </c>
       <c r="E13" t="str">
         <v>N/A</v>
       </c>
       <c r="F13" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G13" t="str">
         <v>Passed</v>
@@ -953,22 +953,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TC-FUN-018</v>
+        <v>TC-UI-016</v>
       </c>
       <c r="B14" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C14" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D14" t="str">
-        <v>Functional logic check element #18</v>
+        <v>Verify style rules for component container #16</v>
       </c>
       <c r="E14" t="str">
         <v>N/A</v>
       </c>
       <c r="F14" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G14" t="str">
         <v>Passed</v>
@@ -979,22 +979,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TC-FUN-019</v>
+        <v>TC-UI-017</v>
       </c>
       <c r="B15" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C15" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D15" t="str">
-        <v>Functional logic check element #19</v>
+        <v>Verify style rules for component container #17</v>
       </c>
       <c r="E15" t="str">
         <v>N/A</v>
       </c>
       <c r="F15" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G15" t="str">
         <v>Passed</v>
@@ -1005,22 +1005,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TC-FUN-020</v>
+        <v>TC-UI-018</v>
       </c>
       <c r="B16" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C16" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D16" t="str">
-        <v>Functional logic check element #20</v>
+        <v>Verify style rules for component container #18</v>
       </c>
       <c r="E16" t="str">
         <v>N/A</v>
       </c>
       <c r="F16" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G16" t="str">
         <v>Passed</v>
@@ -1031,22 +1031,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TC-FUN-021</v>
+        <v>TC-UI-019</v>
       </c>
       <c r="B17" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C17" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D17" t="str">
-        <v>Functional logic check element #21</v>
+        <v>Verify style rules for component container #19</v>
       </c>
       <c r="E17" t="str">
         <v>N/A</v>
       </c>
       <c r="F17" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G17" t="str">
         <v>Passed</v>
@@ -1057,22 +1057,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TC-FUN-022</v>
+        <v>TC-UI-020</v>
       </c>
       <c r="B18" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C18" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D18" t="str">
-        <v>Functional logic check element #22</v>
+        <v>Verify style rules for component container #20</v>
       </c>
       <c r="E18" t="str">
         <v>N/A</v>
       </c>
       <c r="F18" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G18" t="str">
         <v>Passed</v>
@@ -1083,22 +1083,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TC-FUN-023</v>
+        <v>TC-UI-021</v>
       </c>
       <c r="B19" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C19" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D19" t="str">
-        <v>Functional logic check element #23</v>
+        <v>Verify style rules for component container #21</v>
       </c>
       <c r="E19" t="str">
         <v>N/A</v>
       </c>
       <c r="F19" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G19" t="str">
         <v>Passed</v>
@@ -1109,22 +1109,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TC-FUN-024</v>
+        <v>TC-UI-022</v>
       </c>
       <c r="B20" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C20" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D20" t="str">
-        <v>Functional logic check element #24</v>
+        <v>Verify style rules for component container #22</v>
       </c>
       <c r="E20" t="str">
         <v>N/A</v>
       </c>
       <c r="F20" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G20" t="str">
         <v>Passed</v>
@@ -1135,22 +1135,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TC-FUN-025</v>
+        <v>TC-UI-023</v>
       </c>
       <c r="B21" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C21" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D21" t="str">
-        <v>Functional logic check element #25</v>
+        <v>Verify style rules for component container #23</v>
       </c>
       <c r="E21" t="str">
         <v>N/A</v>
       </c>
       <c r="F21" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G21" t="str">
         <v>Passed</v>
@@ -1161,22 +1161,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>TC-FUN-026</v>
+        <v>TC-UI-024</v>
       </c>
       <c r="B22" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C22" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D22" t="str">
-        <v>Functional logic check element #26</v>
+        <v>Verify style rules for component container #24</v>
       </c>
       <c r="E22" t="str">
         <v>N/A</v>
       </c>
       <c r="F22" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G22" t="str">
         <v>Passed</v>
@@ -1187,22 +1187,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TC-FUN-027</v>
+        <v>TC-UI-025</v>
       </c>
       <c r="B23" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C23" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D23" t="str">
-        <v>Functional logic check element #27</v>
+        <v>Verify style rules for component container #25</v>
       </c>
       <c r="E23" t="str">
         <v>N/A</v>
       </c>
       <c r="F23" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G23" t="str">
         <v>Passed</v>
@@ -1213,22 +1213,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TC-FUN-028</v>
+        <v>TC-UI-026</v>
       </c>
       <c r="B24" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C24" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D24" t="str">
-        <v>Functional logic check element #28</v>
+        <v>Verify style rules for component container #26</v>
       </c>
       <c r="E24" t="str">
         <v>N/A</v>
       </c>
       <c r="F24" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G24" t="str">
         <v>Passed</v>
@@ -1239,22 +1239,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TC-FUN-029</v>
+        <v>TC-UI-027</v>
       </c>
       <c r="B25" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C25" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D25" t="str">
-        <v>Functional logic check element #29</v>
+        <v>Verify style rules for component container #27</v>
       </c>
       <c r="E25" t="str">
         <v>N/A</v>
       </c>
       <c r="F25" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G25" t="str">
         <v>Passed</v>
@@ -1265,22 +1265,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TC-FUN-030</v>
+        <v>TC-UI-028</v>
       </c>
       <c r="B26" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C26" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D26" t="str">
-        <v>Functional logic check element #30</v>
+        <v>Verify style rules for component container #28</v>
       </c>
       <c r="E26" t="str">
         <v>N/A</v>
       </c>
       <c r="F26" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G26" t="str">
         <v>Passed</v>
@@ -1291,22 +1291,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TC-FUN-031</v>
+        <v>TC-UI-029</v>
       </c>
       <c r="B27" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C27" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D27" t="str">
-        <v>Functional logic check element #31</v>
+        <v>Verify style rules for component container #29</v>
       </c>
       <c r="E27" t="str">
         <v>N/A</v>
       </c>
       <c r="F27" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G27" t="str">
         <v>Passed</v>
@@ -1317,111 +1317,33 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>TC-FUN-032</v>
+        <v>TC-UI-030</v>
       </c>
       <c r="B28" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C28" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D28" t="str">
-        <v>Functional logic check element #32</v>
+        <v>Verify style rules for component container #30</v>
       </c>
       <c r="E28" t="str">
         <v>N/A</v>
       </c>
       <c r="F28" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G28" t="str">
         <v>Passed</v>
       </c>
       <c r="H28" t="str">
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>TC-FUN-033</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Functional Testing</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Telemetry</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Functional logic check element #33</v>
-      </c>
-      <c r="E29" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Verification completes with success status</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>TC-FUN-034</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Functional Testing</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Telemetry</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Functional logic check element #34</v>
-      </c>
-      <c r="E30" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Verification completes with success status</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>TC-FUN-035</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Functional Testing</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Telemetry</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Functional logic check element #35</v>
-      </c>
-      <c r="E31" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Verification completes with success status</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H31" t="str">
         <v>Passed</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H28"/>
   </ignoredErrors>
 </worksheet>
 </file>